--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.89986166812962</v>
+        <v>3.071227521071063</v>
       </c>
       <c r="D2" t="n">
-        <v>18.74624090000937</v>
+        <v>3.046264146251522</v>
       </c>
       <c r="E2" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F2" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.56345000894848</v>
+        <v>2.041560626454127</v>
       </c>
       <c r="D3" t="n">
-        <v>12.38261977464983</v>
+        <v>2.012175713380598</v>
       </c>
       <c r="E3" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F3" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.94310612681715</v>
+        <v>5.840754745607787</v>
       </c>
       <c r="D4" t="n">
-        <v>35.75259464901011</v>
+        <v>5.809796630464144</v>
       </c>
       <c r="E4" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F4" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.42747352172684</v>
+        <v>4.294464447280611</v>
       </c>
       <c r="D5" t="n">
-        <v>26.30307339013942</v>
+        <v>4.274249425897656</v>
       </c>
       <c r="E5" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F5" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.41343827920075</v>
+        <v>6.892183720370122</v>
       </c>
       <c r="D6" t="n">
-        <v>42.44925598101132</v>
+        <v>6.89800409691434</v>
       </c>
       <c r="E6" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F6" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.22815373213323</v>
+        <v>5.72457498147165</v>
       </c>
       <c r="D7" t="n">
-        <v>35.08052025216247</v>
+        <v>5.700584540976402</v>
       </c>
       <c r="E7" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F7" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.94613071131914</v>
+        <v>8.603746240589361</v>
       </c>
       <c r="D8" t="n">
-        <v>53.0996861027735</v>
+        <v>8.628698991700693</v>
       </c>
       <c r="E8" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F8" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.36550731369898</v>
+        <v>2.821894938476085</v>
       </c>
       <c r="D9" t="n">
-        <v>17.26068633019088</v>
+        <v>2.804861528656017</v>
       </c>
       <c r="E9" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F9" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.29459081890426</v>
+        <v>2.647871008071943</v>
       </c>
       <c r="D10" t="n">
-        <v>16.10188594078486</v>
+        <v>2.616556465377539</v>
       </c>
       <c r="E10" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F10" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>20.94744140901419</v>
+        <v>3.403959228964806</v>
       </c>
       <c r="D11" t="n">
-        <v>20.74229877321342</v>
+        <v>3.370623550647181</v>
       </c>
       <c r="E11" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F11" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>9.880332995088537</v>
+        <v>1.605554111701887</v>
       </c>
       <c r="D12" t="n">
-        <v>10.01727396770241</v>
+        <v>1.627807019751642</v>
       </c>
       <c r="E12" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F12" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.62837974642471</v>
+        <v>5.302111708794016</v>
       </c>
       <c r="D13" t="n">
-        <v>32.83603228424637</v>
+        <v>5.335855246190036</v>
       </c>
       <c r="E13" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F13" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>13.81655076471973</v>
+        <v>2.245189499266956</v>
       </c>
       <c r="D14" t="n">
-        <v>13.97610687797232</v>
+        <v>2.271117367670502</v>
       </c>
       <c r="E14" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F14" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.62473325362274</v>
+        <v>6.439019153713695</v>
       </c>
       <c r="D15" t="n">
-        <v>39.60760583335392</v>
+        <v>6.436235947920013</v>
       </c>
       <c r="E15" t="n">
-        <v>12.63264252388726</v>
+        <v>2.05280441013168</v>
       </c>
       <c r="F15" t="n">
-        <v>12.66867078353014</v>
+        <v>2.058659002323648</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
